--- a/reports/excel/Execution_Summary.xlsx
+++ b/reports/excel/Execution_Summary.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1921</v>
+        <v>2000</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>96.05%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>96.25%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.02s</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
